--- a/docs/brand/XLOOP_街区品牌勾勒.xlsx
+++ b/docs/brand/XLOOP_街区品牌勾勒.xlsx
@@ -628,22 +628,22 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>总部~2万 + 云谷中位~0.7万</t>
+          <t>总部~2万 + 云谷~0.7万（含农发行金科，同文路对过）+ 浙商2027爬坡约0.2万（康定北，更近吾悦）</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>午餐、下班、团建</t>
+          <t>午餐、下班、团建；农发行过马路保底，浙商和吾悦抢午饭</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>午餐28–48；晚餐70–140；团建100–180/人</t>
+          <t>园区午餐28–48；银行金科可40–60；晚餐70–140；团建100–180/人</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>工作日底盘</t>
+          <t>工作日底盘。规划6000禁止加总当客流</t>
         </is>
       </c>
     </row>
